--- a/tools/importer/reports/import-informational-page.report.xlsx
+++ b/tools/importer/reports/import-informational-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>informational-page</t>
   </si>
   <si>
-    <t>2026-03-25T20:06:44.592Z</t>
+    <t>2026-03-25T21:52:54.987Z</t>
   </si>
   <si>
     <t>About — WKND Adventures</t>
@@ -73,7 +73,7 @@
     <t>hub-landing-page</t>
   </si>
   <si>
-    <t>2026-03-25T19:55:17.888Z</t>
+    <t>2026-03-25T21:52:18.650Z</t>
   </si>
   <si>
     <t>Adventures — WKND Adventures</t>
@@ -94,7 +94,7 @@
     <t>editorial-section-page</t>
   </si>
   <si>
-    <t>2026-03-25T20:03:41.787Z</t>
+    <t>2026-03-25T21:52:43.895Z</t>
   </si>
   <si>
     <t>Community — WKND Adventures</t>
@@ -112,7 +112,7 @@
     <t>wknd/destinations</t>
   </si>
   <si>
-    <t>2026-03-25T19:55:26.332Z</t>
+    <t>2026-03-25T21:52:26.775Z</t>
   </si>
   <si>
     <t>Destinations — WKND Adventures</t>
@@ -130,7 +130,7 @@
     <t>wknd/expeditions</t>
   </si>
   <si>
-    <t>2026-03-25T19:55:22.568Z</t>
+    <t>2026-03-25T21:52:23.144Z</t>
   </si>
   <si>
     <t>Expeditions — WKND Adventures</t>
@@ -148,7 +148,7 @@
     <t>wknd/faq</t>
   </si>
   <si>
-    <t>2026-03-25T20:06:48.903Z</t>
+    <t>2026-03-25T21:52:58.447Z</t>
   </si>
   <si>
     <t>Questions — WKND Adventures</t>
@@ -166,7 +166,7 @@
     <t>wknd/field-notes</t>
   </si>
   <si>
-    <t>2026-03-25T20:03:37.901Z</t>
+    <t>2026-03-25T21:52:39.092Z</t>
   </si>
   <si>
     <t>Field Notes — WKND Adventures</t>
@@ -184,7 +184,7 @@
     <t>wknd/gear</t>
   </si>
   <si>
-    <t>2026-03-25T19:55:30.024Z</t>
+    <t>2026-03-25T21:52:30.926Z</t>
   </si>
   <si>
     <t>Gear — WKND Adventures</t>
@@ -205,7 +205,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-25T19:36:34.437Z</t>
+    <t>2026-03-25T21:51:39.187Z</t>
   </si>
   <si>
     <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
@@ -223,7 +223,7 @@
     <t>wknd/sustainability</t>
   </si>
   <si>
-    <t>2026-03-25T20:03:45.652Z</t>
+    <t>2026-03-25T21:52:46.949Z</t>
   </si>
   <si>
     <t>Wild Ethics — WKND Adventures</t>
@@ -244,7 +244,7 @@
     <t>blog-article</t>
   </si>
   <si>
-    <t>2026-03-25T19:51:09.783Z</t>
+    <t>2026-03-25T21:51:56.885Z</t>
   </si>
   <si>
     <t>Six Days Through the High Alps — WKND Adventures</t>
@@ -259,7 +259,7 @@
     <t>wknd/blog/kayaking-norway</t>
   </si>
   <si>
-    <t>2026-03-25T19:51:05.765Z</t>
+    <t>2026-03-25T21:51:52.173Z</t>
   </si>
   <si>
     <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
@@ -274,7 +274,7 @@
     <t>wknd/blog/mountain-photography</t>
   </si>
   <si>
-    <t>2026-03-25T19:51:18.776Z</t>
+    <t>2026-03-25T21:52:06.182Z</t>
   </si>
   <si>
     <t>The Camera on Your Back — WKND Adventures</t>
@@ -289,7 +289,7 @@
     <t>wknd/blog/patagonia-trek</t>
   </si>
   <si>
-    <t>2026-03-25T19:50:59.980Z</t>
+    <t>2026-03-25T21:51:47.181Z</t>
   </si>
   <si>
     <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
@@ -304,7 +304,7 @@
     <t>wknd/blog/ultralight-backpacking</t>
   </si>
   <si>
-    <t>2026-03-25T19:51:23.139Z</t>
+    <t>2026-03-25T21:52:10.428Z</t>
   </si>
   <si>
     <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
@@ -319,7 +319,7 @@
     <t>wknd/blog/yosemite-rock-climbing</t>
   </si>
   <si>
-    <t>2026-03-25T19:51:13.281Z</t>
+    <t>2026-03-25T21:52:00.868Z</t>
   </si>
   <si>
     <t>First Light on the Valley — WKND Adventures</t>

--- a/tools/importer/reports/import-informational-page.report.xlsx
+++ b/tools/importer/reports/import-informational-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>informational-page</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:54.987Z</t>
+    <t>2026-03-25T22:39:19.774Z</t>
   </si>
   <si>
     <t>About — WKND Adventures</t>
@@ -73,7 +73,7 @@
     <t>hub-landing-page</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:18.650Z</t>
+    <t>2026-03-25T22:38:50.170Z</t>
   </si>
   <si>
     <t>Adventures — WKND Adventures</t>
@@ -94,7 +94,7 @@
     <t>editorial-section-page</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:43.895Z</t>
+    <t>2026-03-25T22:39:12.692Z</t>
   </si>
   <si>
     <t>Community — WKND Adventures</t>
@@ -112,7 +112,7 @@
     <t>wknd/destinations</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:26.775Z</t>
+    <t>2026-03-25T22:39:00.255Z</t>
   </si>
   <si>
     <t>Destinations — WKND Adventures</t>
@@ -130,7 +130,7 @@
     <t>wknd/expeditions</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:23.144Z</t>
+    <t>2026-03-25T22:38:54.411Z</t>
   </si>
   <si>
     <t>Expeditions — WKND Adventures</t>
@@ -148,7 +148,7 @@
     <t>wknd/faq</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:58.447Z</t>
+    <t>2026-03-25T22:39:24.754Z</t>
   </si>
   <si>
     <t>Questions — WKND Adventures</t>
@@ -166,7 +166,7 @@
     <t>wknd/field-notes</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:39.092Z</t>
+    <t>2026-03-25T22:39:08.351Z</t>
   </si>
   <si>
     <t>Field Notes — WKND Adventures</t>
@@ -184,7 +184,7 @@
     <t>wknd/gear</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:30.926Z</t>
+    <t>2026-03-25T22:39:05.395Z</t>
   </si>
   <si>
     <t>Gear — WKND Adventures</t>
@@ -205,7 +205,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-25T21:51:39.187Z</t>
+    <t>2026-03-25T22:38:22.396Z</t>
   </si>
   <si>
     <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
@@ -223,7 +223,7 @@
     <t>wknd/sustainability</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:46.949Z</t>
+    <t>2026-03-25T22:39:15.900Z</t>
   </si>
   <si>
     <t>Wild Ethics — WKND Adventures</t>
@@ -244,7 +244,7 @@
     <t>blog-article</t>
   </si>
   <si>
-    <t>2026-03-25T21:51:56.885Z</t>
+    <t>2026-03-25T22:38:32.623Z</t>
   </si>
   <si>
     <t>Six Days Through the High Alps — WKND Adventures</t>
@@ -259,7 +259,7 @@
     <t>wknd/blog/kayaking-norway</t>
   </si>
   <si>
-    <t>2026-03-25T21:51:52.173Z</t>
+    <t>2026-03-25T22:38:28.755Z</t>
   </si>
   <si>
     <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
@@ -274,7 +274,7 @@
     <t>wknd/blog/mountain-photography</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:06.182Z</t>
+    <t>2026-03-25T22:38:41.925Z</t>
   </si>
   <si>
     <t>The Camera on Your Back — WKND Adventures</t>
@@ -289,7 +289,7 @@
     <t>wknd/blog/patagonia-trek</t>
   </si>
   <si>
-    <t>2026-03-25T21:51:47.181Z</t>
+    <t>2026-03-25T22:38:25.204Z</t>
   </si>
   <si>
     <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
@@ -304,7 +304,7 @@
     <t>wknd/blog/ultralight-backpacking</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:10.428Z</t>
+    <t>2026-03-25T22:38:45.800Z</t>
   </si>
   <si>
     <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
@@ -319,7 +319,7 @@
     <t>wknd/blog/yosemite-rock-climbing</t>
   </si>
   <si>
-    <t>2026-03-25T21:52:00.868Z</t>
+    <t>2026-03-25T22:38:37.044Z</t>
   </si>
   <si>
     <t>First Light on the Valley — WKND Adventures</t>
